--- a/Student_Site_Data.xlsx
+++ b/Student_Site_Data.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Ln947o18ZlRAd/D/ZGIDQTageDKz4g9RkTjm62h69P4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Ko6nWKuNhyYajFQrf9iLLKxI+cNL3DpoIEITEXo3r9Q="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="269">
   <si>
     <t>Timestamp</t>
   </si>
@@ -602,18 +602,6 @@
     <t>Julian</t>
   </si>
   <si>
-    <t>STU1037</t>
-  </si>
-  <si>
-    <t>stu1037@bcit.ca</t>
-  </si>
-  <si>
-    <t>Turner</t>
-  </si>
-  <si>
-    <t>Addison</t>
-  </si>
-  <si>
     <t>STU1038</t>
   </si>
   <si>
@@ -647,18 +635,6 @@
     <t>Samuel</t>
   </si>
   <si>
-    <t>STU1041</t>
-  </si>
-  <si>
-    <t>stu1041@bcit.ca</t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
-    <t>Penelope</t>
-  </si>
-  <si>
     <t>STU1042</t>
   </si>
   <si>
@@ -693,30 +669,6 @@
   </si>
   <si>
     <t>Andrew</t>
-  </si>
-  <si>
-    <t>STU1045</t>
-  </si>
-  <si>
-    <t>stu1045@bcit.ca</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>Aria</t>
-  </si>
-  <si>
-    <t>STU1046</t>
-  </si>
-  <si>
-    <t>stu1046@bcit.ca</t>
-  </si>
-  <si>
-    <t>Morris</t>
-  </si>
-  <si>
-    <t>John</t>
   </si>
   <si>
     <t>STU1047</t>
@@ -2432,22 +2384,22 @@
         <v>197</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -2462,58 +2414,58 @@
         <v>200</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="K40" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -2534,19 +2486,19 @@
         <v>17</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -2564,22 +2516,22 @@
         <v>212</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -2600,19 +2552,19 @@
         <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -2675,16 +2627,18 @@
         <v>45</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1" t="s">
+      <c r="A46" s="1" t="s">
         <v>225</v>
+      </c>
+      <c r="B46" s="1">
+        <v>638205.0</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>226</v>
@@ -2696,164 +2650,34 @@
         <v>228</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>95</v>
+        <v>229</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C47" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B50" s="1">
-        <v>638205.0</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
+    </row>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
@@ -3798,10 +3622,6 @@
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -3830,31 +3650,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2">
@@ -4152,7 +3972,7 @@
         <v>1011.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C12" s="1" t="b">
         <v>1</v>
@@ -4210,7 +4030,7 @@
         <v>1014.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="b">
         <v>1</v>
@@ -4239,7 +4059,7 @@
         <v>1015.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C15" s="1" t="b">
         <v>1</v>
@@ -4268,7 +4088,7 @@
         <v>1016.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C16" s="1" t="b">
         <v>0</v>
@@ -4471,7 +4291,7 @@
         <v>1025.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C23" s="1" t="b">
         <v>1</v>
@@ -4500,7 +4320,7 @@
         <v>1026.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C24" s="1" t="b">
         <v>0</v>
@@ -4558,7 +4378,7 @@
         <v>1028.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C26" s="1" t="b">
         <v>1</v>
@@ -4645,7 +4465,7 @@
         <v>1032.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="b">
         <v>1</v>
@@ -4674,7 +4494,7 @@
         <v>1033.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C30" s="1" t="b">
         <v>0</v>
@@ -4790,7 +4610,7 @@
         <v>1042.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C34" s="1" t="b">
         <v>1</v>
@@ -4819,7 +4639,7 @@
         <v>1043.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C35" s="1" t="b">
         <v>0</v>
@@ -4964,7 +4784,7 @@
         <v>1048.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C40" s="1" t="b">
         <v>1</v>
@@ -5022,7 +4842,7 @@
         <v>1050.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C42" s="1" t="b">
         <v>1</v>
@@ -5051,7 +4871,7 @@
         <v>1052.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C43" s="1" t="b">
         <v>1</v>
@@ -5196,7 +5016,7 @@
         <v>1059.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C48" s="1" t="b">
         <v>1</v>
@@ -6326,19 +6146,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2">
@@ -6346,7 +6166,7 @@
         <v>2001.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -6363,7 +6183,7 @@
         <v>2002.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C3" s="1">
         <v>4.0</v>
@@ -6380,7 +6200,7 @@
         <v>2003.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -6397,7 +6217,7 @@
         <v>2004.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C5" s="1">
         <v>5.0</v>
@@ -6414,7 +6234,7 @@
         <v>2005.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -6431,7 +6251,7 @@
         <v>2006.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C7" s="1">
         <v>3.0</v>
@@ -6448,7 +6268,7 @@
         <v>2007.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="C8" s="1">
         <v>4.0</v>
@@ -6465,7 +6285,7 @@
         <v>2008.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -6482,7 +6302,7 @@
         <v>2009.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="C10" s="1">
         <v>4.0</v>
@@ -6499,7 +6319,7 @@
         <v>2010.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -6516,7 +6336,7 @@
         <v>2011.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C12" s="1">
         <v>5.0</v>
@@ -6533,7 +6353,7 @@
         <v>2012.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -6550,7 +6370,7 @@
         <v>2013.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -6567,7 +6387,7 @@
         <v>2014.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -6584,7 +6404,7 @@
         <v>2015.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>

--- a/Student_Site_Data.xlsx
+++ b/Student_Site_Data.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Ko6nWKuNhyYajFQrf9iLLKxI+cNL3DpoIEITEXo3r9Q="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="rKt0BFjzQ4vfqoNKPvynKrWKL2yxw7VVTYG4Z/Id+aA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="262">
   <si>
     <t>Timestamp</t>
   </si>
@@ -74,693 +74,717 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>St.Paul's</t>
+  </si>
+  <si>
+    <t>Royal Columbian</t>
+  </si>
+  <si>
+    <t>Medray</t>
+  </si>
+  <si>
+    <t>Greig Associates</t>
+  </si>
+  <si>
+    <t>BCWH</t>
+  </si>
+  <si>
+    <t>STU1002</t>
+  </si>
+  <si>
+    <t>stu1002@bcit.ca</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Brooke Burnaby</t>
+  </si>
+  <si>
+    <t>WCMI</t>
+  </si>
+  <si>
+    <t>NSMI</t>
+  </si>
+  <si>
+    <t>STU1003</t>
+  </si>
+  <si>
+    <t>stu1003@bcit.ca</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>Cardiac</t>
+  </si>
+  <si>
+    <t>Vancouver General/UBC</t>
+  </si>
+  <si>
+    <t>Surrey</t>
+  </si>
+  <si>
+    <t>Abbotsford</t>
+  </si>
+  <si>
+    <t>STU1004</t>
+  </si>
+  <si>
+    <t>stu1004@bcit.ca</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Kamloops (RIH)</t>
+  </si>
+  <si>
+    <t>Lindsay Diagnostics Kamloops</t>
+  </si>
+  <si>
+    <t>Kelowna KGH</t>
+  </si>
+  <si>
+    <t>Vernon</t>
+  </si>
+  <si>
+    <t>Salmon Arm (SLDH)</t>
+  </si>
+  <si>
+    <t>Kamloops, Kelowna</t>
+  </si>
+  <si>
+    <t>STU1005</t>
+  </si>
+  <si>
+    <t>stu1005@bcit.ca</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Olivia</t>
+  </si>
+  <si>
+    <t>VMI Abbotsford/Langley</t>
+  </si>
+  <si>
+    <t>Brooke Richmond</t>
+  </si>
+  <si>
+    <t>STU1006</t>
+  </si>
+  <si>
+    <t>stu1006@bcit.ca</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Langley</t>
+  </si>
+  <si>
+    <t>STU1007</t>
+  </si>
+  <si>
+    <t>stu1007@bcit.ca</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>Ava</t>
+  </si>
+  <si>
+    <t>Lions Gate</t>
+  </si>
+  <si>
+    <t>Richmond</t>
+  </si>
+  <si>
+    <t>Burnaby</t>
+  </si>
+  <si>
+    <t>STU1008</t>
+  </si>
+  <si>
+    <t>stu1008@bcit.ca</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>Vernon Radiology Associates</t>
+  </si>
+  <si>
+    <t>Penticton</t>
+  </si>
+  <si>
+    <t>Kelowna, Vernon</t>
+  </si>
+  <si>
+    <t>STU1009</t>
+  </si>
+  <si>
+    <t>stu1009@bcit.ca</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>NSMI Squamish</t>
+  </si>
+  <si>
+    <t>North Van</t>
+  </si>
+  <si>
+    <t>STU1010</t>
+  </si>
+  <si>
+    <t>stu1010@bcit.ca</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Royal Jubilee</t>
+  </si>
+  <si>
+    <t>Island ultrasound</t>
+  </si>
+  <si>
+    <t>Nanaimo</t>
+  </si>
+  <si>
+    <t>Oceanside (Parksville)</t>
+  </si>
+  <si>
+    <t>Victoria, Nanaimo</t>
+  </si>
+  <si>
+    <t>STU1011</t>
+  </si>
+  <si>
+    <t>stu1011@bcit.ca</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Peace Arch</t>
+  </si>
+  <si>
+    <t>STU1012</t>
+  </si>
+  <si>
+    <t>stu1012@bcit.ca</t>
+  </si>
+  <si>
+    <t>Harris</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>KMI</t>
+  </si>
+  <si>
+    <t>Penticton, Kelowna</t>
+  </si>
+  <si>
+    <t>STU1013</t>
+  </si>
+  <si>
+    <t>stu1013@bcit.ca</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Amelia</t>
+  </si>
+  <si>
+    <t>STU1014</t>
+  </si>
+  <si>
+    <t>stu1014@bcit.ca</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
     <t>Vancouver General</t>
   </si>
   <si>
-    <t>Burnaby</t>
-  </si>
-  <si>
-    <t>Richmond</t>
-  </si>
-  <si>
-    <t>Surrey</t>
-  </si>
-  <si>
-    <t>Kamloops (RIH)</t>
-  </si>
-  <si>
-    <t>Kamloops, Kelowna</t>
-  </si>
-  <si>
-    <t>STU1002</t>
-  </si>
-  <si>
-    <t>stu1002@bcit.ca</t>
-  </si>
-  <si>
-    <t>Jones</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Abbotsford</t>
-  </si>
-  <si>
-    <t>STU1003</t>
-  </si>
-  <si>
-    <t>stu1003@bcit.ca</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>Sophia</t>
-  </si>
-  <si>
-    <t>Cardiac</t>
-  </si>
-  <si>
-    <t>St.Paul's</t>
-  </si>
-  <si>
-    <t>Royal Columbian</t>
-  </si>
-  <si>
-    <t>Vancouver General/UBC</t>
-  </si>
-  <si>
-    <t>BCWH</t>
-  </si>
-  <si>
-    <t>Vancouver</t>
-  </si>
-  <si>
-    <t>STU1004</t>
-  </si>
-  <si>
-    <t>stu1004@bcit.ca</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Kelowna KGH</t>
-  </si>
-  <si>
-    <t>Vernon</t>
-  </si>
-  <si>
-    <t>Victoria</t>
+    <t>Priority for BCWH</t>
+  </si>
+  <si>
+    <t>STU1015</t>
+  </si>
+  <si>
+    <t>stu1015@bcit.ca</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>STU1016</t>
+  </si>
+  <si>
+    <t>stu1016@bcit.ca</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>Logan</t>
+  </si>
+  <si>
+    <t>Kamloops</t>
+  </si>
+  <si>
+    <t>STU1017</t>
+  </si>
+  <si>
+    <t>stu1017@bcit.ca</t>
+  </si>
+  <si>
+    <t>Robinson</t>
+  </si>
+  <si>
+    <t>Harper</t>
+  </si>
+  <si>
+    <t>STU1018</t>
+  </si>
+  <si>
+    <t>stu1018@bcit.ca</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Comox</t>
+  </si>
+  <si>
+    <t>STU1019</t>
+  </si>
+  <si>
+    <t>stu1019@bcit.ca</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>STU1020</t>
+  </si>
+  <si>
+    <t>stu1020@bcit.ca</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>STU1021</t>
+  </si>
+  <si>
+    <t>stu1021@bcit.ca</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>STU1022</t>
+  </si>
+  <si>
+    <t>stu1022@bcit.ca</t>
+  </si>
+  <si>
+    <t>Walker</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>UBC General</t>
+  </si>
+  <si>
+    <t>STU1023</t>
+  </si>
+  <si>
+    <t>stu1023@bcit.ca</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Wants BCWH</t>
+  </si>
+  <si>
+    <t>STU1024</t>
+  </si>
+  <si>
+    <t>stu1024@bcit.ca</t>
+  </si>
+  <si>
+    <t>Allen</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>STU1025</t>
+  </si>
+  <si>
+    <t>stu1025@bcit.ca</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>STU1026</t>
+  </si>
+  <si>
+    <t>stu1026@bcit.ca</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Campbell River</t>
+  </si>
+  <si>
+    <t>Comox, Campbell River</t>
+  </si>
+  <si>
+    <t>STU1027</t>
+  </si>
+  <si>
+    <t>stu1027@bcit.ca</t>
+  </si>
+  <si>
+    <t>Wright</t>
+  </si>
+  <si>
+    <t>Mila</t>
+  </si>
+  <si>
+    <t>STU1028</t>
+  </si>
+  <si>
+    <t>stu1028@bcit.ca</t>
+  </si>
+  <si>
+    <t>Scott</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>Kelowna</t>
+  </si>
+  <si>
+    <t>STU1029</t>
+  </si>
+  <si>
+    <t>stu1029@bcit.ca</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Scarlett</t>
+  </si>
+  <si>
+    <t>STU1030</t>
+  </si>
+  <si>
+    <t>stu1030@bcit.ca</t>
+  </si>
+  <si>
+    <t>Baker</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
+    <t>STU1031</t>
+  </si>
+  <si>
+    <t>stu1031@bcit.ca</t>
+  </si>
+  <si>
+    <t>Adams</t>
+  </si>
+  <si>
+    <t>Chloe</t>
+  </si>
+  <si>
+    <t>STU1032</t>
+  </si>
+  <si>
+    <t>stu1032@bcit.ca</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>Jack</t>
   </si>
   <si>
     <t>Prince George (UHNBC)</t>
   </si>
   <si>
-    <t>Kamloops, Kelowna, Vernon</t>
-  </si>
-  <si>
-    <t>STU1005</t>
-  </si>
-  <si>
-    <t>stu1005@bcit.ca</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t>Olivia</t>
+    <t>Prince George, Kamloops</t>
+  </si>
+  <si>
+    <t>STU1033</t>
+  </si>
+  <si>
+    <t>stu1033@bcit.ca</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>Lily</t>
+  </si>
+  <si>
+    <t>STU1034</t>
+  </si>
+  <si>
+    <t>stu1034@bcit.ca</t>
+  </si>
+  <si>
+    <t>Mitchell</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Duncan (CDH)</t>
+  </si>
+  <si>
+    <t>STU1035</t>
+  </si>
+  <si>
+    <t>stu1035@bcit.ca</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>Zoey</t>
+  </si>
+  <si>
+    <t>STU1036</t>
+  </si>
+  <si>
+    <t>stu1036@bcit.ca</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t>STU1038</t>
+  </si>
+  <si>
+    <t>stu1038@bcit.ca</t>
+  </si>
+  <si>
+    <t>Phillips</t>
+  </si>
+  <si>
+    <t>Grayson</t>
+  </si>
+  <si>
+    <t>STU1039</t>
+  </si>
+  <si>
+    <t>stu1039@bcit.ca</t>
+  </si>
+  <si>
+    <t>Campbell</t>
+  </si>
+  <si>
+    <t>STU1040</t>
+  </si>
+  <si>
+    <t>stu1040@bcit.ca</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>STU1042</t>
+  </si>
+  <si>
+    <t>stu1042@bcit.ca</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>Levi</t>
+  </si>
+  <si>
+    <t>STU1043</t>
+  </si>
+  <si>
+    <t>stu1043@bcit.ca</t>
+  </si>
+  <si>
+    <t>Collins</t>
+  </si>
+  <si>
+    <t>Hannah</t>
+  </si>
+  <si>
+    <t>STU1044</t>
+  </si>
+  <si>
+    <t>stu1044@bcit.ca</t>
+  </si>
+  <si>
+    <t>Stewart</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>STU1047</t>
+  </si>
+  <si>
+    <t>stu1047@bcit.ca</t>
+  </si>
+  <si>
+    <t>Rogers</t>
+  </si>
+  <si>
+    <t>Layla</t>
+  </si>
+  <si>
+    <t>Eagle Ridge</t>
+  </si>
+  <si>
+    <t>STU1048</t>
+  </si>
+  <si>
+    <t>stu1048@bcit.ca</t>
+  </si>
+  <si>
+    <t>Reed</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>site_id</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>is_general</t>
+  </si>
+  <si>
+    <t>is_cardiac</t>
+  </si>
+  <si>
+    <t>is_dual</t>
+  </si>
+  <si>
+    <t>high_acuity</t>
+  </si>
+  <si>
+    <t>out_of_town</t>
+  </si>
+  <si>
+    <t>only_may_to_dec</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>Chilliwack</t>
+  </si>
+  <si>
+    <t>Cranbrook (EKRH)</t>
   </si>
   <si>
     <t>Delta</t>
   </si>
   <si>
-    <t>Chilliwack</t>
-  </si>
-  <si>
-    <t>STU1006</t>
-  </si>
-  <si>
-    <t>stu1006@bcit.ca</t>
-  </si>
-  <si>
-    <t>Wilson</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>STU1007</t>
-  </si>
-  <si>
-    <t>stu1007@bcit.ca</t>
-  </si>
-  <si>
-    <t>Taylor</t>
-  </si>
-  <si>
-    <t>Ava</t>
-  </si>
-  <si>
-    <t>STU1008</t>
-  </si>
-  <si>
-    <t>stu1008@bcit.ca</t>
-  </si>
-  <si>
-    <t>Anderson</t>
-  </si>
-  <si>
-    <t>Noah</t>
-  </si>
-  <si>
-    <t>Nanaimo</t>
-  </si>
-  <si>
-    <t>Kelowna, Vernon</t>
-  </si>
-  <si>
-    <t>STU1009</t>
-  </si>
-  <si>
-    <t>stu1009@bcit.ca</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>Isabella</t>
-  </si>
-  <si>
-    <t>STU1010</t>
-  </si>
-  <si>
-    <t>stu1010@bcit.ca</t>
-  </si>
-  <si>
-    <t>Jackson</t>
-  </si>
-  <si>
-    <t>Liam</t>
-  </si>
-  <si>
-    <t>Comox</t>
-  </si>
-  <si>
-    <t>Campbell River</t>
-  </si>
-  <si>
-    <t>Royal Jubilee</t>
-  </si>
-  <si>
-    <t>Victoria, Nanaimo</t>
-  </si>
-  <si>
-    <t>STU1011</t>
-  </si>
-  <si>
-    <t>stu1011@bcit.ca</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>STU1012</t>
-  </si>
-  <si>
-    <t>stu1012@bcit.ca</t>
-  </si>
-  <si>
-    <t>Harris</t>
-  </si>
-  <si>
-    <t>Ethan</t>
-  </si>
-  <si>
-    <t>Penticton</t>
-  </si>
-  <si>
-    <t>Salmon Arm (SLDH)</t>
-  </si>
-  <si>
-    <t>STU1013</t>
-  </si>
-  <si>
-    <t>stu1013@bcit.ca</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>Amelia</t>
-  </si>
-  <si>
-    <t>Langley</t>
-  </si>
-  <si>
     <t>Mission</t>
   </si>
   <si>
-    <t>STU1014</t>
-  </si>
-  <si>
-    <t>stu1014@bcit.ca</t>
-  </si>
-  <si>
-    <t>Thompson</t>
-  </si>
-  <si>
-    <t>Mason</t>
-  </si>
-  <si>
-    <t>STU1015</t>
-  </si>
-  <si>
-    <t>stu1015@bcit.ca</t>
-  </si>
-  <si>
-    <t>Garcia</t>
-  </si>
-  <si>
-    <t>Mia</t>
-  </si>
-  <si>
-    <t>STU1016</t>
-  </si>
-  <si>
-    <t>stu1016@bcit.ca</t>
-  </si>
-  <si>
-    <t>Martinez</t>
-  </si>
-  <si>
-    <t>Logan</t>
-  </si>
-  <si>
-    <t>Kamloops, Vernon</t>
-  </si>
-  <si>
-    <t>STU1017</t>
-  </si>
-  <si>
-    <t>stu1017@bcit.ca</t>
-  </si>
-  <si>
-    <t>Robinson</t>
-  </si>
-  <si>
-    <t>Harper</t>
-  </si>
-  <si>
-    <t>STU1018</t>
-  </si>
-  <si>
-    <t>stu1018@bcit.ca</t>
-  </si>
-  <si>
-    <t>Clark</t>
-  </si>
-  <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>STU1019</t>
-  </si>
-  <si>
-    <t>stu1019@bcit.ca</t>
-  </si>
-  <si>
-    <t>Rodriguez</t>
-  </si>
-  <si>
-    <t>Abigail</t>
-  </si>
-  <si>
-    <t>STU1020</t>
-  </si>
-  <si>
-    <t>stu1020@bcit.ca</t>
-  </si>
-  <si>
-    <t>Lewis</t>
-  </si>
-  <si>
-    <t>Benjamin</t>
-  </si>
-  <si>
-    <t>Kelowna, Penticton</t>
-  </si>
-  <si>
-    <t>STU1021</t>
-  </si>
-  <si>
-    <t>stu1021@bcit.ca</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>STU1022</t>
-  </si>
-  <si>
-    <t>stu1022@bcit.ca</t>
-  </si>
-  <si>
-    <t>Walker</t>
-  </si>
-  <si>
-    <t>Lucas</t>
-  </si>
-  <si>
-    <t>STU1023</t>
-  </si>
-  <si>
-    <t>stu1023@bcit.ca</t>
-  </si>
-  <si>
-    <t>Hall</t>
-  </si>
-  <si>
-    <t>Sofia</t>
-  </si>
-  <si>
-    <t>STU1024</t>
-  </si>
-  <si>
-    <t>stu1024@bcit.ca</t>
-  </si>
-  <si>
-    <t>Allen</t>
-  </si>
-  <si>
-    <t>Alexander</t>
-  </si>
-  <si>
-    <t>Kamloops, Victoria</t>
-  </si>
-  <si>
-    <t>STU1025</t>
-  </si>
-  <si>
-    <t>stu1025@bcit.ca</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Emily</t>
-  </si>
-  <si>
-    <t>STU1026</t>
-  </si>
-  <si>
-    <t>stu1026@bcit.ca</t>
-  </si>
-  <si>
-    <t>King</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Nanaimo;Comox</t>
-  </si>
-  <si>
-    <t>STU1027</t>
-  </si>
-  <si>
-    <t>stu1027@bcit.ca</t>
-  </si>
-  <si>
-    <t>Wright</t>
-  </si>
-  <si>
-    <t>Mila</t>
-  </si>
-  <si>
-    <t>STU1028</t>
-  </si>
-  <si>
-    <t>stu1028@bcit.ca</t>
-  </si>
-  <si>
-    <t>Scott</t>
-  </si>
-  <si>
-    <t>Henry</t>
-  </si>
-  <si>
-    <t>STU1029</t>
-  </si>
-  <si>
-    <t>stu1029@bcit.ca</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Scarlett</t>
-  </si>
-  <si>
-    <t>STU1030</t>
-  </si>
-  <si>
-    <t>stu1030@bcit.ca</t>
-  </si>
-  <si>
-    <t>Baker</t>
-  </si>
-  <si>
-    <t>Sebastian</t>
-  </si>
-  <si>
-    <t>STU1031</t>
-  </si>
-  <si>
-    <t>stu1031@bcit.ca</t>
-  </si>
-  <si>
-    <t>Adams</t>
-  </si>
-  <si>
-    <t>Chloe</t>
-  </si>
-  <si>
-    <t>STU1032</t>
-  </si>
-  <si>
-    <t>stu1032@bcit.ca</t>
-  </si>
-  <si>
-    <t>Nelson</t>
-  </si>
-  <si>
-    <t>Jack</t>
-  </si>
-  <si>
-    <t>Prince George</t>
-  </si>
-  <si>
-    <t>STU1033</t>
-  </si>
-  <si>
-    <t>stu1033@bcit.ca</t>
-  </si>
-  <si>
-    <t>Carter</t>
-  </si>
-  <si>
-    <t>Lily</t>
-  </si>
-  <si>
-    <t>STU1034</t>
-  </si>
-  <si>
-    <t>stu1034@bcit.ca</t>
-  </si>
-  <si>
-    <t>Mitchell</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>STU1035</t>
-  </si>
-  <si>
-    <t>stu1035@bcit.ca</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>Zoey</t>
-  </si>
-  <si>
-    <t>STU1036</t>
-  </si>
-  <si>
-    <t>stu1036@bcit.ca</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>Julian</t>
-  </si>
-  <si>
-    <t>STU1038</t>
-  </si>
-  <si>
-    <t>stu1038@bcit.ca</t>
-  </si>
-  <si>
-    <t>Phillips</t>
-  </si>
-  <si>
-    <t>Grayson</t>
-  </si>
-  <si>
-    <t>STU1039</t>
-  </si>
-  <si>
-    <t>stu1039@bcit.ca</t>
-  </si>
-  <si>
-    <t>Campbell</t>
-  </si>
-  <si>
-    <t>STU1040</t>
-  </si>
-  <si>
-    <t>stu1040@bcit.ca</t>
-  </si>
-  <si>
-    <t>Parker</t>
-  </si>
-  <si>
-    <t>Samuel</t>
-  </si>
-  <si>
-    <t>STU1042</t>
-  </si>
-  <si>
-    <t>stu1042@bcit.ca</t>
-  </si>
-  <si>
-    <t>Edwards</t>
-  </si>
-  <si>
-    <t>Levi</t>
-  </si>
-  <si>
-    <t>STU1043</t>
-  </si>
-  <si>
-    <t>stu1043@bcit.ca</t>
-  </si>
-  <si>
-    <t>Collins</t>
-  </si>
-  <si>
-    <t>Hannah</t>
-  </si>
-  <si>
-    <t>STU1044</t>
-  </si>
-  <si>
-    <t>stu1044@bcit.ca</t>
-  </si>
-  <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>STU1047</t>
-  </si>
-  <si>
-    <t>stu1047@bcit.ca</t>
-  </si>
-  <si>
-    <t>Rogers</t>
-  </si>
-  <si>
-    <t>Layla</t>
-  </si>
-  <si>
-    <t>STU1048</t>
-  </si>
-  <si>
-    <t>stu1048@bcit.ca</t>
-  </si>
-  <si>
-    <t>Reed</t>
-  </si>
-  <si>
-    <t>Luke</t>
-  </si>
-  <si>
-    <t>2025/12/24 12:51:12 PM PST</t>
-  </si>
-  <si>
-    <t>Test@bcit.ca</t>
-  </si>
-  <si>
-    <t>Kathie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bron </t>
-  </si>
-  <si>
-    <t>Lions Gate</t>
-  </si>
-  <si>
-    <t>WCMI Kerrisdale</t>
-  </si>
-  <si>
-    <t>Campbell River;Nanaimo;Salmon Arm (SLDH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher </t>
-  </si>
-  <si>
-    <t>site_id</t>
-  </si>
-  <si>
-    <t>site_name</t>
-  </si>
-  <si>
-    <t>is_general</t>
-  </si>
-  <si>
-    <t>is_cardiac</t>
-  </si>
-  <si>
-    <t>is_dual</t>
-  </si>
-  <si>
-    <t>high_acuity</t>
-  </si>
-  <si>
-    <t>out_of_town</t>
-  </si>
-  <si>
-    <t>only_may_to_dec</t>
-  </si>
-  <si>
-    <t>capacity</t>
-  </si>
-  <si>
-    <t>Cranbrook (EKRH)</t>
-  </si>
-  <si>
-    <t>Duncan (CDH)</t>
-  </si>
-  <si>
-    <t>Eagle Ridge</t>
-  </si>
-  <si>
     <t>MSJ</t>
   </si>
   <si>
-    <t>Peace Arch</t>
-  </si>
-  <si>
     <t>Ridge Meadows</t>
   </si>
   <si>
@@ -773,9 +797,6 @@
     <t>Squamish</t>
   </si>
   <si>
-    <t>UBC General</t>
-  </si>
-  <si>
     <t>clinic_id</t>
   </si>
   <si>
@@ -783,55 +804,13 @@
   </si>
   <si>
     <t>days_per_week</t>
-  </si>
-  <si>
-    <t>Brooke Burnaby</t>
-  </si>
-  <si>
-    <t>Brooke Richmond</t>
-  </si>
-  <si>
-    <t>Greig Associates</t>
-  </si>
-  <si>
-    <t>Island ultrasound</t>
-  </si>
-  <si>
-    <t>KMI R</t>
-  </si>
-  <si>
-    <t>KMI Westside</t>
-  </si>
-  <si>
-    <t>Lindsay Diagnostics Kamloops</t>
-  </si>
-  <si>
-    <t>Medray</t>
-  </si>
-  <si>
-    <t>NSMI</t>
-  </si>
-  <si>
-    <t>NSMI Squamish</t>
-  </si>
-  <si>
-    <t>Oceanside (Parksville)</t>
-  </si>
-  <si>
-    <t>Vernon Radiology Associates</t>
-  </si>
-  <si>
-    <t>VMI Abbotsford/Langley</t>
-  </si>
-  <si>
-    <t>WCMI Hornby</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -843,6 +822,16 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -852,18 +841,41 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1105,1574 +1117,1637 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K10" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="L10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="K14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="G16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="L24" s="2"/>
+      <c r="M24" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="K31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K33" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L33" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="L45" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="M45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" s="1">
-        <v>638205.0</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -3577,51 +3652,6 @@
     <row r="947" ht="15.75" customHeight="1"/>
     <row r="948" ht="15.75" customHeight="1"/>
     <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -3649,32 +3679,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>234</v>
+      <c r="A1" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2">
@@ -3682,7 +3712,7 @@
         <v>1001.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="b">
         <v>1</v>
@@ -3711,7 +3741,7 @@
         <v>1002.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="b">
         <v>0</v>
@@ -3740,7 +3770,7 @@
         <v>1003.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>1</v>
@@ -3769,7 +3799,7 @@
         <v>1004.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1" t="b">
         <v>0</v>
@@ -3798,7 +3828,7 @@
         <v>1005.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="b">
         <v>1</v>
@@ -3827,7 +3857,7 @@
         <v>1006.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="C7" s="1" t="b">
         <v>1</v>
@@ -3856,7 +3886,7 @@
         <v>1007.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="C8" s="1" t="b">
         <v>0</v>
@@ -3885,7 +3915,7 @@
         <v>1008.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>250</v>
       </c>
       <c r="C9" s="1" t="b">
         <v>1</v>
@@ -3914,7 +3944,7 @@
         <v>1009.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>1</v>
@@ -3943,7 +3973,7 @@
         <v>1010.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="b">
         <v>0</v>
@@ -3972,7 +4002,7 @@
         <v>1011.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C12" s="1" t="b">
         <v>1</v>
@@ -4001,7 +4031,7 @@
         <v>1013.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>252</v>
       </c>
       <c r="C13" s="1" t="b">
         <v>1</v>
@@ -4030,7 +4060,7 @@
         <v>1014.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="C14" s="1" t="b">
         <v>1</v>
@@ -4059,7 +4089,7 @@
         <v>1015.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C15" s="1" t="b">
         <v>1</v>
@@ -4088,7 +4118,7 @@
         <v>1016.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C16" s="1" t="b">
         <v>0</v>
@@ -4117,7 +4147,7 @@
         <v>1018.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="b">
         <v>1</v>
@@ -4146,7 +4176,7 @@
         <v>1019.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="b">
         <v>0</v>
@@ -4175,7 +4205,7 @@
         <v>1020.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="b">
         <v>1</v>
@@ -4204,7 +4234,7 @@
         <v>1021.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="b">
         <v>0</v>
@@ -4233,7 +4263,7 @@
         <v>1023.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="b">
         <v>1</v>
@@ -4262,7 +4292,7 @@
         <v>1024.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="b">
         <v>0</v>
@@ -4291,7 +4321,7 @@
         <v>1025.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="C23" s="1" t="b">
         <v>1</v>
@@ -4320,7 +4350,7 @@
         <v>1026.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="b">
         <v>0</v>
@@ -4349,7 +4379,7 @@
         <v>1027.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>96</v>
+        <v>253</v>
       </c>
       <c r="C25" s="1" t="b">
         <v>1</v>
@@ -4378,7 +4408,7 @@
         <v>1028.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C26" s="1" t="b">
         <v>1</v>
@@ -4407,7 +4437,7 @@
         <v>1029.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1" t="b">
         <v>1</v>
@@ -4436,7 +4466,7 @@
         <v>1030.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="b">
         <v>0</v>
@@ -4465,7 +4495,7 @@
         <v>1032.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>246</v>
+        <v>94</v>
       </c>
       <c r="C29" s="1" t="b">
         <v>1</v>
@@ -4494,7 +4524,7 @@
         <v>1033.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>94</v>
       </c>
       <c r="C30" s="1" t="b">
         <v>0</v>
@@ -4523,7 +4553,7 @@
         <v>1034.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="b">
         <v>1</v>
@@ -4552,7 +4582,7 @@
         <v>1035.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="b">
         <v>0</v>
@@ -4581,7 +4611,7 @@
         <v>1041.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C33" s="1" t="b">
         <v>1</v>
@@ -4610,7 +4640,7 @@
         <v>1042.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C34" s="1" t="b">
         <v>1</v>
@@ -4639,7 +4669,7 @@
         <v>1043.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C35" s="1" t="b">
         <v>0</v>
@@ -4668,7 +4698,7 @@
         <v>1044.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C36" s="1" t="b">
         <v>1</v>
@@ -4697,7 +4727,7 @@
         <v>1045.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1" t="b">
         <v>0</v>
@@ -4726,7 +4756,7 @@
         <v>1046.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="b">
         <v>1</v>
@@ -4755,7 +4785,7 @@
         <v>1047.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="b">
         <v>0</v>
@@ -4784,7 +4814,7 @@
         <v>1048.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C40" s="1" t="b">
         <v>1</v>
@@ -4813,7 +4843,7 @@
         <v>1049.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C41" s="1" t="b">
         <v>1</v>
@@ -4842,7 +4872,7 @@
         <v>1050.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C42" s="1" t="b">
         <v>1</v>
@@ -4871,7 +4901,7 @@
         <v>1052.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C43" s="1" t="b">
         <v>1</v>
@@ -4900,7 +4930,7 @@
         <v>1053.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C44" s="1" t="b">
         <v>1</v>
@@ -4929,7 +4959,7 @@
         <v>1054.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1" t="b">
         <v>0</v>
@@ -4958,7 +4988,7 @@
         <v>1055.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C46" s="1" t="b">
         <v>1</v>
@@ -4987,7 +5017,7 @@
         <v>1056.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C47" s="1" t="b">
         <v>0</v>
@@ -5016,7 +5046,7 @@
         <v>1059.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>251</v>
+        <v>145</v>
       </c>
       <c r="C48" s="1" t="b">
         <v>1</v>
@@ -5045,7 +5075,7 @@
         <v>1060.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="b">
         <v>1</v>
@@ -5074,7 +5104,7 @@
         <v>1061.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1" t="b">
         <v>0</v>
@@ -5103,7 +5133,7 @@
         <v>1063.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C51" s="1" t="b">
         <v>1</v>
@@ -5132,7 +5162,7 @@
         <v>1064.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C52" s="1" t="b">
         <v>0</v>
@@ -5161,7 +5191,7 @@
         <v>1065.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C53" s="1" t="b">
         <v>1</v>
@@ -5190,7 +5220,7 @@
         <v>1066.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C54" s="1" t="b">
         <v>0</v>
@@ -6145,20 +6175,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>239</v>
+      <c r="A1" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
@@ -6166,7 +6196,7 @@
         <v>2001.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -6183,7 +6213,7 @@
         <v>2002.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1">
         <v>4.0</v>
@@ -6200,7 +6230,7 @@
         <v>2003.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -6217,7 +6247,7 @@
         <v>2004.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1">
         <v>5.0</v>
@@ -6234,7 +6264,7 @@
         <v>2005.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -6248,13 +6278,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>2006.0</v>
+        <v>2007.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>260</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>1</v>
@@ -6265,16 +6295,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>2007.0</v>
+        <v>2008.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="b">
         <v>0</v>
@@ -6282,13 +6312,13 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>2008.0</v>
+        <v>2009.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>262</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>0</v>
@@ -6299,16 +6329,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>2009.0</v>
+        <v>2010.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="C10" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="b">
         <v>0</v>
@@ -6316,50 +6346,50 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>2010.0</v>
+        <v>2011.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>2011.0</v>
+        <v>2012.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="C12" s="1">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>2012.0</v>
+        <v>2013.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D13" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="b">
         <v>0</v>
@@ -6367,10 +6397,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>2013.0</v>
+        <v>2014.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>267</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -6382,40 +6412,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>2014.0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1">
-        <v>2015.0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -7394,8 +7392,6 @@
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
